--- a/medidor de metricas/automatizacion_completa/metricas_resultados_pc.xlsx
+++ b/medidor de metricas/automatizacion_completa/metricas_resultados_pc.xlsx
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>44.81</v>
+        <v>44.77</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>71.05</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="K12" t="n">
         <v>1.86</v>
@@ -2984,13 +2984,13 @@
         <v>231</v>
       </c>
       <c r="C12" t="n">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="D12" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="E12" t="n">
-        <v>3026</v>
+        <v>3022</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>13.1</v>
+        <v>13.08</v>
       </c>
     </row>
   </sheetData>
@@ -3363,16 +3363,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3026</v>
+        <v>3022</v>
       </c>
       <c r="C12" t="n">
         <v>231</v>
       </c>
       <c r="D12" t="n">
-        <v>21000</v>
+        <v>20977</v>
       </c>
       <c r="E12" t="n">
-        <v>44.81</v>
+        <v>44.77</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D12" t="n">
-        <v>71.05</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="E12" t="n">
         <v>1.86</v>
@@ -4014,14 +4014,14 @@
         <v>31</v>
       </c>
       <c r="J12" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="K12" t="n">
         <v>123</v>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>missing-function-docstring: 39; trailing-whitespace: 23; no-member: 14; broad-exception-caught: 11; unexpected-keyword-arg: 9; 6/5: 8; 104/100: 7; undefined-variable: 6; protected-access: 5; 106/100: 4</t>
+          <t>missing-function-docstring: 39; trailing-whitespace: 21; no-member: 14; broad-exception-caught: 11; unused-import: 9; unexpected-keyword-arg: 9; 6/5: 8; 104/100: 7; undefined-variable: 6; protected-access: 5</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4522,19 +4522,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Propio</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4546,7 +4533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4977,21 +4964,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Propio</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5003,7 +4975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W12"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5918,35 +5890,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Propio</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
-      <c r="L12" s="5" t="inlineStr"/>
-      <c r="M12" s="5" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" s="7" t="inlineStr"/>
-      <c r="Q12" s="7" t="inlineStr"/>
-      <c r="R12" s="7" t="inlineStr"/>
-      <c r="S12" s="7" t="inlineStr"/>
-      <c r="T12" s="5" t="inlineStr"/>
-      <c r="U12" s="7" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/medidor de metricas/automatizacion_completa/metricas_resultados_pc.xlsx
+++ b/medidor de metricas/automatizacion_completa/metricas_resultados_pc.xlsx
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>44.77</v>
+        <v>44.71</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>73.45999999999999</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
@@ -2984,13 +2984,13 @@
         <v>231</v>
       </c>
       <c r="C12" t="n">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="D12" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="E12" t="n">
-        <v>3022</v>
+        <v>3040</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>13.08</v>
+        <v>13.16</v>
       </c>
     </row>
   </sheetData>
@@ -3363,16 +3363,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3022</v>
+        <v>3040</v>
       </c>
       <c r="C12" t="n">
         <v>231</v>
       </c>
       <c r="D12" t="n">
-        <v>20977</v>
+        <v>21069</v>
       </c>
       <c r="E12" t="n">
-        <v>44.77</v>
+        <v>44.71</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3987,13 +3987,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D12" t="n">
-        <v>73.45999999999999</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -4011,17 +4011,17 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K12" t="n">
         <v>123</v>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>missing-function-docstring: 39; trailing-whitespace: 21; no-member: 14; broad-exception-caught: 11; unused-import: 9; unexpected-keyword-arg: 9; 6/5: 8; 104/100: 7; undefined-variable: 6; protected-access: 5</t>
+          <t>missing-function-docstring: 39; trailing-whitespace: 21; no-member: 16; broad-exception-caught: 11; unused-import: 9; unexpected-keyword-arg: 9; 6/5: 8; 104/100: 7; undefined-variable: 6; protected-access: 5</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4058,57 +4058,6 @@
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Error</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Propio</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Analizador metricas</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Análisis concurrencia: No se encontró el código 'Propio' en Concurrencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Propio</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Analizador metricas</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Análisis tokens: No se encontró el código 'Propio' en Datos Tokens</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Propio</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Analizador metricas</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Análisis CPU/memoria: No se encontró el código 'Propio' en CPU_Memoria</t>
         </is>
       </c>
     </row>

--- a/medidor de metricas/automatizacion_completa/metricas_resultados_pc.xlsx
+++ b/medidor de metricas/automatizacion_completa/metricas_resultados_pc.xlsx
@@ -27,11 +27,26 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00\%"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="00008000"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -84,18 +99,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1692,61 +1712,61 @@
           <t>Java</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="4" t="n">
         <v>1.45</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="4" t="n">
         <v>50.45</v>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>Buena</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="4" t="n">
         <v>16.19</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="4" t="n">
         <v>3.5</v>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>Presencia de issues altos</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>Muy buen uso de concurrencia</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="O2" s="4" t="n">
         <v>59.75</v>
       </c>
-      <c r="P2" s="4" t="inlineStr">
+      <c r="P2" s="5" t="inlineStr">
         <is>
           <t>Alto NLOC/token, ajustada por refinamientos.</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="n">
+      <c r="Q2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="R2" s="5" t="inlineStr">
         <is>
           <t>Consumo bajo de CPU</t>
         </is>
       </c>
-      <c r="S2" s="5" t="n">
+      <c r="S2" s="6" t="n">
         <v>1.26953125</v>
       </c>
-      <c r="T2" s="4" t="inlineStr">
+      <c r="T2" s="5" t="inlineStr">
         <is>
           <t>Consumo bajo de CPU</t>
         </is>
@@ -1778,61 +1798,61 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="4" t="n">
         <v>2.74</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="4" t="n">
         <v>42.6</v>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Buena</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="4" t="n">
         <v>176.16</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="4" t="n">
         <v>2.28</v>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>Predominan issues medios</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="4" t="n">
         <v>2.75</v>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>Hay aspectos que requieren observación</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="O3" s="4" t="n">
         <v>0.06</v>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>Bajo NLOC/token, ajustada por refinamientos.</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="n">
+      <c r="Q3" s="6" t="n">
         <v>6.25</v>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>Consumo bajo de CPU</t>
         </is>
       </c>
-      <c r="S3" s="5" t="n">
+      <c r="S3" s="6" t="n">
         <v>1.66015625</v>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="T3" s="5" t="inlineStr">
         <is>
           <t>Consumo bajo de CPU</t>
         </is>
@@ -1864,61 +1884,61 @@
           <t>Java</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="4" t="n">
         <v>2.18</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="4" t="n">
         <v>47.23</v>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Buena</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="4" t="n">
         <v>77.20999999999999</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="4" t="n">
         <v>3.59</v>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>Presencia de issues altos</t>
         </is>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>Muy buen uso de concurrencia</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="O4" s="4" t="n">
         <v>6.55</v>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>Bajo NLOC/token, ajustada por refinamientos.</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="n">
+      <c r="Q4" s="6" t="n">
         <v>5.25</v>
       </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>Consumo bajo de CPU</t>
         </is>
       </c>
-      <c r="S4" s="5" t="n">
+      <c r="S4" s="6" t="n">
         <v>2.9052734375</v>
       </c>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="T4" s="5" t="inlineStr">
         <is>
           <t>Consumo bajo de CPU</t>
         </is>
@@ -1950,61 +1970,61 @@
           <t>Java</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="4" t="n">
         <v>2.84</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="4" t="n">
         <v>51.53</v>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Buena</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="4" t="n">
         <v>78.7</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="4" t="n">
         <v>2.47</v>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>Predominan issues medios</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>Muy buen uso de concurrencia</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="O5" s="4" t="n">
         <v>2.68</v>
       </c>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="P5" s="5" t="inlineStr">
         <is>
           <t>Bajo NLOC/token, ajustada por refinamientos.</t>
         </is>
       </c>
-      <c r="Q5" s="5" t="n">
+      <c r="Q5" s="6" t="n">
         <v>5.25</v>
       </c>
-      <c r="R5" s="4" t="inlineStr">
+      <c r="R5" s="5" t="inlineStr">
         <is>
           <t>Consumo bajo de CPU</t>
         </is>
       </c>
-      <c r="S5" s="5" t="n">
+      <c r="S5" s="6" t="n">
         <v>2.9052734375</v>
       </c>
-      <c r="T5" s="4" t="inlineStr">
+      <c r="T5" s="5" t="inlineStr">
         <is>
           <t>Consumo bajo de CPU</t>
         </is>
@@ -2036,61 +2056,61 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="4" t="n">
         <v>2.6</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="4" t="n">
         <v>29.23</v>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="4" t="n">
         <v>370.59</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="4" t="n">
         <v>1.29</v>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>Predominan issues bajos</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="4" t="n">
         <v>2.75</v>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>Hay aspectos que requieren observación</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="O6" s="4" t="n">
         <v>60.71</v>
       </c>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
         <is>
           <t>Alto NLOC/token, ajustada por refinamientos.</t>
         </is>
       </c>
-      <c r="Q6" s="5" t="n">
+      <c r="Q6" s="6" t="n">
         <v>0.125</v>
       </c>
-      <c r="R6" s="4" t="inlineStr">
+      <c r="R6" s="5" t="inlineStr">
         <is>
           <t>Consumo bajo de CPU</t>
         </is>
       </c>
-      <c r="S6" s="5" t="n">
+      <c r="S6" s="6" t="n">
         <v>0.48828125</v>
       </c>
-      <c r="T6" s="4" t="inlineStr">
+      <c r="T6" s="5" t="inlineStr">
         <is>
           <t>Consumo bajo de CPU</t>
         </is>
@@ -2122,61 +2142,61 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="4" t="n">
         <v>2.32</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="4" t="n">
         <v>22.05</v>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="4" t="n">
         <v>157.56</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="4" t="n">
         <v>1.9</v>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Predominan issues medios</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="4" t="n">
         <v>2.75</v>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Hay aspectos que requieren observación</t>
         </is>
       </c>
-      <c r="O7" t="n">
+      <c r="O7" s="4" t="n">
         <v>38.11</v>
       </c>
-      <c r="P7" s="4" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>Alto NLOC/token, ajustada por refinamientos.</t>
         </is>
       </c>
-      <c r="Q7" s="5" t="n">
+      <c r="Q7" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="R7" s="4" t="inlineStr">
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>Consumo bajo de CPU</t>
         </is>
       </c>
-      <c r="S7" s="5" t="n">
+      <c r="S7" s="6" t="n">
         <v>0.3662109375</v>
       </c>
-      <c r="T7" s="4" t="inlineStr">
+      <c r="T7" s="5" t="inlineStr">
         <is>
           <t>Consumo bajo de CPU</t>
         </is>
@@ -2208,61 +2228,61 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="4" t="n">
         <v>3.4</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="4" t="n">
         <v>25.98</v>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="4" t="n">
         <v>248.83</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="4" t="n">
         <v>1.47</v>
       </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>Predominan issues bajos</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="N8" s="5" t="inlineStr">
         <is>
           <t>Requiere revisión</t>
         </is>
       </c>
-      <c r="O8" t="n">
+      <c r="O8" s="4" t="n">
         <v>35.77</v>
       </c>
-      <c r="P8" s="4" t="inlineStr">
+      <c r="P8" s="5" t="inlineStr">
         <is>
           <t>Alto NLOC/token, ajustada por refinamientos.</t>
         </is>
       </c>
-      <c r="Q8" s="5" t="n">
+      <c r="Q8" s="6" t="n">
         <v>2.6525</v>
       </c>
-      <c r="R8" s="4" t="inlineStr">
+      <c r="R8" s="5" t="inlineStr">
         <is>
           <t>Consumo bajo de CPU</t>
         </is>
       </c>
-      <c r="S8" s="5" t="n">
+      <c r="S8" s="6" t="n">
         <v>0.48828125</v>
       </c>
-      <c r="T8" s="4" t="inlineStr">
+      <c r="T8" s="5" t="inlineStr">
         <is>
           <t>Consumo bajo de CPU</t>
         </is>
@@ -2294,61 +2314,61 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="4" t="n">
         <v>3.29</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="4" t="n">
         <v>21.91</v>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="4" t="n">
         <v>141.07</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="4" t="n">
         <v>1.73</v>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>Predominan issues medios</t>
         </is>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>Requiere revisión</t>
         </is>
       </c>
-      <c r="O9" t="n">
+      <c r="O9" s="4" t="n">
         <v>47.83</v>
       </c>
-      <c r="P9" s="4" t="inlineStr">
+      <c r="P9" s="5" t="inlineStr">
         <is>
           <t>Alto NLOC/token, ajustada por refinamientos.</t>
         </is>
       </c>
-      <c r="Q9" s="5" t="n">
+      <c r="Q9" s="6" t="n">
         <v>1.55375</v>
       </c>
-      <c r="R9" s="4" t="inlineStr">
+      <c r="R9" s="5" t="inlineStr">
         <is>
           <t>Consumo bajo de CPU</t>
         </is>
       </c>
-      <c r="S9" s="5" t="n">
+      <c r="S9" s="6" t="n">
         <v>0.48828125</v>
       </c>
-      <c r="T9" s="4" t="inlineStr">
+      <c r="T9" s="5" t="inlineStr">
         <is>
           <t>Consumo bajo de CPU</t>
         </is>
@@ -2380,61 +2400,61 @@
           <t>Java</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="4" t="n">
         <v>2.25</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="4" t="n">
         <v>41.7</v>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Buena</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="4" t="n">
         <v>26.47</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="4" t="n">
         <v>1.96</v>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>Predominan issues medios</t>
         </is>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>Muy buen uso de concurrencia</t>
         </is>
       </c>
-      <c r="O10" t="n">
+      <c r="O10" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="P10" s="4" t="inlineStr">
+      <c r="P10" s="5" t="inlineStr">
         <is>
           <t>Bajo NLOC/token, ajustada por refinamientos.</t>
         </is>
       </c>
-      <c r="Q10" s="5" t="n">
+      <c r="Q10" s="6" t="n">
         <v>25.41625</v>
       </c>
-      <c r="R10" s="4" t="inlineStr">
+      <c r="R10" s="5" t="inlineStr">
         <is>
           <t>Consumo medio de CPU</t>
         </is>
       </c>
-      <c r="S10" s="5" t="n">
+      <c r="S10" s="6" t="n">
         <v>2.44140625</v>
       </c>
-      <c r="T10" s="4" t="inlineStr">
+      <c r="T10" s="5" t="inlineStr">
         <is>
           <t>Consumo bajo de CPU</t>
         </is>
@@ -2466,61 +2486,61 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="4" t="n">
         <v>1.7</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="4" t="n">
         <v>52.77</v>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>Buena</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>Presencia de issues altos</t>
         </is>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" s="4" t="n">
         <v>2.75</v>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>Hay aspectos que requieren observación</t>
         </is>
       </c>
-      <c r="O11" t="n">
+      <c r="O11" s="4" t="n">
         <v>135.38</v>
       </c>
-      <c r="P11" s="4" t="inlineStr">
+      <c r="P11" s="5" t="inlineStr">
         <is>
           <t>Alto NLOC/token, ajustada por refinamientos.</t>
         </is>
       </c>
-      <c r="Q11" s="5" t="n">
+      <c r="Q11" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="R11" s="4" t="inlineStr">
+      <c r="R11" s="5" t="inlineStr">
         <is>
           <t>Consumo medio de CPU</t>
         </is>
       </c>
-      <c r="S11" s="5" t="n">
+      <c r="S11" s="6" t="n">
         <v>2.4169921875</v>
       </c>
-      <c r="T11" s="4" t="inlineStr">
+      <c r="T11" s="5" t="inlineStr">
         <is>
           <t>Consumo bajo de CPU</t>
         </is>
@@ -2552,41 +2572,73 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="F12" s="4" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="H12" t="n">
-        <v>44.71</v>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="n">
+        <v>44.69</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>Buena</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>74.01000000000001</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="J12" s="4" t="n">
+        <v>74.11</v>
+      </c>
+      <c r="K12" s="4" t="n">
         <v>1.89</v>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>Predominan issues medios</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="5" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="5" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Q12" s="9" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="R12" s="8" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S12" s="9" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2984,13 +3036,13 @@
         <v>231</v>
       </c>
       <c r="C12" t="n">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="D12" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="E12" t="n">
-        <v>3040</v>
+        <v>3063</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3003,7 +3055,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>13.16</v>
+        <v>13.26</v>
       </c>
     </row>
   </sheetData>
@@ -3363,16 +3415,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3040</v>
+        <v>3063</v>
       </c>
       <c r="C12" t="n">
         <v>231</v>
       </c>
       <c r="D12" t="n">
-        <v>21069</v>
+        <v>21182</v>
       </c>
       <c r="E12" t="n">
-        <v>44.71</v>
+        <v>44.69</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3519,7 +3571,7 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L2" s="10" t="inlineStr">
         <is>
           <t>AvoidUsingVolatile: 2; ControlStatementBraces: 1; UseLocaleWithCaseConversions: 1</t>
         </is>
@@ -3569,7 +3621,7 @@
       <c r="K3" t="n">
         <v>70</v>
       </c>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="L3" s="10" t="inlineStr">
         <is>
           <t>missing-function-docstring: 40; import-error: 39; unused-variable: 13; logging-fstring-interpolation: 12; missing-module-docstring: 11; missing-class-docstring: 8; f-string-without-interpolation: 8; broad-exception-caught: 7; wrong-import-order: 7; global-statement: 3</t>
         </is>
@@ -3619,7 +3671,7 @@
       <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="L4" s="10" t="inlineStr">
         <is>
           <t>GuardLogStatement: 22; CloseResource: 8; ControlStatementBraces: 4; LooseCoupling: 3; UseLocaleWithCaseConversions: 2; OneDeclarationPerLine: 1; UncommentedEmptyConstructor: 1</t>
         </is>
@@ -3669,7 +3721,7 @@
       <c r="K5" t="n">
         <v>5</v>
       </c>
-      <c r="L5" s="6" t="inlineStr">
+      <c r="L5" s="10" t="inlineStr">
         <is>
           <t>ControlStatementBraces: 13; GuardLogStatement: 7; LooseCoupling: 5; CloseResource: 3; UselessParentheses: 3; OneDeclarationPerLine: 2; UncommentedEmptyConstructor: 1</t>
         </is>
@@ -3719,7 +3771,7 @@
       <c r="K6" t="n">
         <v>45</v>
       </c>
-      <c r="L6" s="6" t="inlineStr">
+      <c r="L6" s="10" t="inlineStr">
         <is>
           <t>trailing-whitespace: 34; logging-fstring-interpolation: 10; invalid-name: 5; line 306: 4; 105/100: 1; 108/100: 1; 104/100: 1; 107/100: 1; missing-final-newline: 1; missing-module-docstring: 1</t>
         </is>
@@ -3769,7 +3821,7 @@
       <c r="K7" t="n">
         <v>5</v>
       </c>
-      <c r="L7" s="6" t="inlineStr">
+      <c r="L7" s="10" t="inlineStr">
         <is>
           <t>logging-fstring-interpolation: 27; 6/5: 6; 7/5: 4; 10/7: 2; consider-using-max-builtin: 2; 111/100: 1; 123/100: 1; 115/100: 1; missing-class-docstring: 1; 9/7: 1</t>
         </is>
@@ -3819,7 +3871,7 @@
       <c r="K8" t="n">
         <v>28</v>
       </c>
-      <c r="L8" s="6" t="inlineStr">
+      <c r="L8" s="10" t="inlineStr">
         <is>
           <t>logging-fstring-interpolation: 5; broad-exception-caught: 4; 6/5: 4; 101/100: 3; 146/100: 2; 1/2: 2; 7/5: 2; 8/5: 2; 9/5: 2; unused-import: 2</t>
         </is>
@@ -3869,7 +3921,7 @@
       <c r="K9" t="n">
         <v>12</v>
       </c>
-      <c r="L9" s="6" t="inlineStr">
+      <c r="L9" s="10" t="inlineStr">
         <is>
           <t>logging-fstring-interpolation: 21; missing-function-docstring: 5; broad-exception-caught: 4; 6/5: 4; 105/100: 1; 125/100: 1; 119/100: 1; 147/100: 1; 102/100: 1; missing-class-docstring: 1</t>
         </is>
@@ -3919,7 +3971,7 @@
       <c r="K10" t="n">
         <v>13</v>
       </c>
-      <c r="L10" s="6" t="inlineStr">
+      <c r="L10" s="10" t="inlineStr">
         <is>
           <t>PackageCase: 46; UnusedPrivateField: 38; ForLoopCanBeForeach: 25; LooseCoupling: 19; CloseResource: 10; UselessParentheses: 7; CompareObjectsWithEquals: 6; UnusedFormalParameter: 5; UnnecessaryFullyQualifiedName: 4; UncommentedEmptyMethodBody: 3</t>
         </is>
@@ -3969,7 +4021,7 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="6" t="inlineStr">
+      <c r="L11" s="10" t="inlineStr">
         <is>
           <t>import-error: 2; 1/2: 2; fixme: 1; 6/5: 1</t>
         </is>
@@ -3987,10 +4039,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D12" t="n">
-        <v>74.01000000000001</v>
+        <v>74.11</v>
       </c>
       <c r="E12" t="n">
         <v>1.89</v>
@@ -4014,12 +4066,12 @@
         <v>33</v>
       </c>
       <c r="J12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K12" t="n">
-        <v>123</v>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
+        <v>124</v>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
         <is>
           <t>missing-function-docstring: 39; trailing-whitespace: 21; no-member: 16; broad-exception-caught: 11; unused-import: 9; unexpected-keyword-arg: 9; 6/5: 8; 104/100: 7; undefined-variable: 6; protected-access: 5</t>
         </is>
@@ -5094,19 +5146,19 @@
         <v>4</v>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="11" t="n">
         <v>4</v>
       </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n">
+      <c r="I2" s="11" t="n"/>
+      <c r="J2" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="K2" s="5" t="n"/>
-      <c r="L2" s="5" t="n">
+      <c r="K2" s="11" t="n"/>
+      <c r="L2" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="M2" s="5" t="n">
+      <c r="M2" s="11" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
@@ -5119,20 +5171,20 @@
           <t>Consumo bajo de CPU</t>
         </is>
       </c>
-      <c r="P2" s="7" t="n">
+      <c r="P2" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="Q2" s="7" t="n"/>
-      <c r="R2" s="7" t="n">
+      <c r="Q2" s="12" t="n"/>
+      <c r="R2" s="12" t="n">
         <v>4096</v>
       </c>
-      <c r="S2" s="7" t="n">
+      <c r="S2" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="T2" s="5" t="n">
+      <c r="T2" s="11" t="n">
         <v>1.26953125</v>
       </c>
-      <c r="U2" s="7" t="n">
+      <c r="U2" s="12" t="n">
         <v>52</v>
       </c>
       <c r="V2" t="inlineStr">
@@ -5171,19 +5223,19 @@
         <v>8</v>
       </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="11" t="n">
         <v>50</v>
       </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n">
+      <c r="I3" s="11" t="n"/>
+      <c r="J3" s="11" t="n">
         <v>6.25</v>
       </c>
-      <c r="K3" s="5" t="n"/>
-      <c r="L3" s="5" t="n">
+      <c r="K3" s="11" t="n"/>
+      <c r="L3" s="11" t="n">
         <v>6.25</v>
       </c>
-      <c r="M3" s="5" t="n">
+      <c r="M3" s="11" t="n">
         <v>6.25</v>
       </c>
       <c r="N3" t="inlineStr">
@@ -5196,20 +5248,20 @@
           <t>Consumo bajo de CPU</t>
         </is>
       </c>
-      <c r="P3" s="7" t="n">
+      <c r="P3" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="Q3" s="7" t="n"/>
-      <c r="R3" s="7" t="n">
+      <c r="Q3" s="12" t="n"/>
+      <c r="R3" s="12" t="n">
         <v>4096</v>
       </c>
-      <c r="S3" s="7" t="n">
+      <c r="S3" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="T3" s="5" t="n">
+      <c r="T3" s="11" t="n">
         <v>1.66015625</v>
       </c>
-      <c r="U3" s="7" t="n">
+      <c r="U3" s="12" t="n">
         <v>68</v>
       </c>
       <c r="V3" t="inlineStr">
@@ -5248,19 +5300,19 @@
         <v>8</v>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="11" t="n">
         <v>42</v>
       </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n">
+      <c r="I4" s="11" t="n"/>
+      <c r="J4" s="11" t="n">
         <v>5.25</v>
       </c>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n">
+      <c r="K4" s="11" t="n"/>
+      <c r="L4" s="11" t="n">
         <v>5.25</v>
       </c>
-      <c r="M4" s="5" t="n">
+      <c r="M4" s="11" t="n">
         <v>5.25</v>
       </c>
       <c r="N4" t="inlineStr">
@@ -5273,20 +5325,20 @@
           <t>Consumo bajo de CPU</t>
         </is>
       </c>
-      <c r="P4" s="7" t="n">
+      <c r="P4" s="12" t="n">
         <v>238</v>
       </c>
-      <c r="Q4" s="7" t="n"/>
-      <c r="R4" s="7" t="n">
+      <c r="Q4" s="12" t="n"/>
+      <c r="R4" s="12" t="n">
         <v>8192</v>
       </c>
-      <c r="S4" s="7" t="n">
+      <c r="S4" s="12" t="n">
         <v>238</v>
       </c>
-      <c r="T4" s="5" t="n">
+      <c r="T4" s="11" t="n">
         <v>2.9052734375</v>
       </c>
-      <c r="U4" s="7" t="n">
+      <c r="U4" s="12" t="n">
         <v>238</v>
       </c>
       <c r="V4" t="inlineStr">
@@ -5325,19 +5377,19 @@
         <v>8</v>
       </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="11" t="n">
         <v>42</v>
       </c>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n">
+      <c r="I5" s="11" t="n"/>
+      <c r="J5" s="11" t="n">
         <v>5.25</v>
       </c>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n">
+      <c r="K5" s="11" t="n"/>
+      <c r="L5" s="11" t="n">
         <v>5.25</v>
       </c>
-      <c r="M5" s="5" t="n">
+      <c r="M5" s="11" t="n">
         <v>5.25</v>
       </c>
       <c r="N5" t="inlineStr">
@@ -5350,20 +5402,20 @@
           <t>Consumo bajo de CPU</t>
         </is>
       </c>
-      <c r="P5" s="7" t="n">
+      <c r="P5" s="12" t="n">
         <v>238</v>
       </c>
-      <c r="Q5" s="7" t="n"/>
-      <c r="R5" s="7" t="n">
+      <c r="Q5" s="12" t="n"/>
+      <c r="R5" s="12" t="n">
         <v>8192</v>
       </c>
-      <c r="S5" s="7" t="n">
+      <c r="S5" s="12" t="n">
         <v>238</v>
       </c>
-      <c r="T5" s="5" t="n">
+      <c r="T5" s="11" t="n">
         <v>2.9052734375</v>
       </c>
-      <c r="U5" s="7" t="n">
+      <c r="U5" s="12" t="n">
         <v>238</v>
       </c>
       <c r="V5" t="inlineStr">
@@ -5402,19 +5454,19 @@
         <v>4</v>
       </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="11" t="n">
         <v>0.5</v>
       </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n">
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="11" t="n">
         <v>0.125</v>
       </c>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n">
+      <c r="K6" s="11" t="n"/>
+      <c r="L6" s="11" t="n">
         <v>0.125</v>
       </c>
-      <c r="M6" s="5" t="n">
+      <c r="M6" s="11" t="n">
         <v>0.125</v>
       </c>
       <c r="N6" t="inlineStr">
@@ -5427,20 +5479,20 @@
           <t>Consumo bajo de CPU</t>
         </is>
       </c>
-      <c r="P6" s="7" t="n">
+      <c r="P6" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="Q6" s="7" t="n"/>
-      <c r="R6" s="7" t="n">
+      <c r="Q6" s="12" t="n"/>
+      <c r="R6" s="12" t="n">
         <v>4096</v>
       </c>
-      <c r="S6" s="7" t="n">
+      <c r="S6" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="T6" s="5" t="n">
+      <c r="T6" s="11" t="n">
         <v>0.48828125</v>
       </c>
-      <c r="U6" s="7" t="n">
+      <c r="U6" s="12" t="n">
         <v>20</v>
       </c>
       <c r="V6" t="inlineStr">
@@ -5479,19 +5531,19 @@
         <v>4</v>
       </c>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="11" t="n">
         <v>0.2</v>
       </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n">
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n">
+      <c r="K7" s="11" t="n"/>
+      <c r="L7" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="M7" s="5" t="n">
+      <c r="M7" s="11" t="n">
         <v>0.05</v>
       </c>
       <c r="N7" t="inlineStr">
@@ -5504,20 +5556,20 @@
           <t>Consumo bajo de CPU</t>
         </is>
       </c>
-      <c r="P7" s="7" t="n">
+      <c r="P7" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="Q7" s="7" t="n"/>
-      <c r="R7" s="7" t="n">
+      <c r="Q7" s="12" t="n"/>
+      <c r="R7" s="12" t="n">
         <v>4096</v>
       </c>
-      <c r="S7" s="7" t="n">
+      <c r="S7" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="T7" s="5" t="n">
+      <c r="T7" s="11" t="n">
         <v>0.3662109375</v>
       </c>
-      <c r="U7" s="7" t="n">
+      <c r="U7" s="12" t="n">
         <v>15</v>
       </c>
       <c r="V7" t="inlineStr">
@@ -5556,19 +5608,19 @@
         <v>4</v>
       </c>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="11" t="n">
         <v>10.61</v>
       </c>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n">
+      <c r="I8" s="11" t="n"/>
+      <c r="J8" s="11" t="n">
         <v>2.6525</v>
       </c>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n">
+      <c r="K8" s="11" t="n"/>
+      <c r="L8" s="11" t="n">
         <v>2.6525</v>
       </c>
-      <c r="M8" s="5" t="n">
+      <c r="M8" s="11" t="n">
         <v>2.6525</v>
       </c>
       <c r="N8" t="inlineStr">
@@ -5581,20 +5633,20 @@
           <t>Consumo bajo de CPU</t>
         </is>
       </c>
-      <c r="P8" s="7" t="n">
+      <c r="P8" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="Q8" s="7" t="n"/>
-      <c r="R8" s="7" t="n">
+      <c r="Q8" s="12" t="n"/>
+      <c r="R8" s="12" t="n">
         <v>4096</v>
       </c>
-      <c r="S8" s="7" t="n">
+      <c r="S8" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="T8" s="5" t="n">
+      <c r="T8" s="11" t="n">
         <v>0.48828125</v>
       </c>
-      <c r="U8" s="7" t="n">
+      <c r="U8" s="12" t="n">
         <v>20</v>
       </c>
       <c r="V8" t="inlineStr">
@@ -5633,19 +5685,19 @@
         <v>8</v>
       </c>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="11" t="n">
         <v>12.43</v>
       </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n">
+      <c r="I9" s="11" t="n"/>
+      <c r="J9" s="11" t="n">
         <v>1.55375</v>
       </c>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n">
+      <c r="K9" s="11" t="n"/>
+      <c r="L9" s="11" t="n">
         <v>1.55375</v>
       </c>
-      <c r="M9" s="5" t="n">
+      <c r="M9" s="11" t="n">
         <v>1.55375</v>
       </c>
       <c r="N9" t="inlineStr">
@@ -5658,20 +5710,20 @@
           <t>Consumo bajo de CPU</t>
         </is>
       </c>
-      <c r="P9" s="7" t="n">
+      <c r="P9" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="Q9" s="7" t="n"/>
-      <c r="R9" s="7" t="n">
+      <c r="Q9" s="12" t="n"/>
+      <c r="R9" s="12" t="n">
         <v>4096</v>
       </c>
-      <c r="S9" s="7" t="n">
+      <c r="S9" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="T9" s="5" t="n">
+      <c r="T9" s="11" t="n">
         <v>0.48828125</v>
       </c>
-      <c r="U9" s="7" t="n">
+      <c r="U9" s="12" t="n">
         <v>20</v>
       </c>
       <c r="V9" t="inlineStr">
@@ -5710,19 +5762,19 @@
         <v>8</v>
       </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="11" t="n">
         <v>203.33</v>
       </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n">
+      <c r="I10" s="11" t="n"/>
+      <c r="J10" s="11" t="n">
         <v>25.41625</v>
       </c>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n">
+      <c r="K10" s="11" t="n"/>
+      <c r="L10" s="11" t="n">
         <v>25.41625</v>
       </c>
-      <c r="M10" s="5" t="n">
+      <c r="M10" s="11" t="n">
         <v>25.41625</v>
       </c>
       <c r="N10" t="inlineStr">
@@ -5735,20 +5787,20 @@
           <t>Consumo medio de CPU</t>
         </is>
       </c>
-      <c r="P10" s="7" t="n">
+      <c r="P10" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="Q10" s="7" t="n"/>
-      <c r="R10" s="7" t="n">
+      <c r="Q10" s="12" t="n"/>
+      <c r="R10" s="12" t="n">
         <v>8192</v>
       </c>
-      <c r="S10" s="7" t="n">
+      <c r="S10" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="T10" s="5" t="n">
+      <c r="T10" s="11" t="n">
         <v>2.44140625</v>
       </c>
-      <c r="U10" s="7" t="n">
+      <c r="U10" s="12" t="n">
         <v>200</v>
       </c>
       <c r="V10" t="inlineStr">
@@ -5787,19 +5839,19 @@
         <v>8</v>
       </c>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="11" t="n">
         <v>304</v>
       </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n">
+      <c r="I11" s="11" t="n"/>
+      <c r="J11" s="11" t="n">
         <v>38</v>
       </c>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n">
+      <c r="K11" s="11" t="n"/>
+      <c r="L11" s="11" t="n">
         <v>38</v>
       </c>
-      <c r="M11" s="5" t="n">
+      <c r="M11" s="11" t="n">
         <v>38</v>
       </c>
       <c r="N11" t="inlineStr">
@@ -5812,20 +5864,20 @@
           <t>Consumo medio de CPU</t>
         </is>
       </c>
-      <c r="P11" s="7" t="n">
+      <c r="P11" s="12" t="n">
         <v>396</v>
       </c>
-      <c r="Q11" s="7" t="n"/>
-      <c r="R11" s="7" t="n">
+      <c r="Q11" s="12" t="n"/>
+      <c r="R11" s="12" t="n">
         <v>16384</v>
       </c>
-      <c r="S11" s="7" t="n">
+      <c r="S11" s="12" t="n">
         <v>396</v>
       </c>
-      <c r="T11" s="5" t="n">
+      <c r="T11" s="11" t="n">
         <v>2.4169921875</v>
       </c>
-      <c r="U11" s="7" t="n">
+      <c r="U11" s="12" t="n">
         <v>396</v>
       </c>
       <c r="V11" t="inlineStr">

--- a/medidor de metricas/automatizacion_completa/metricas_resultados_pc.xlsx
+++ b/medidor de metricas/automatizacion_completa/metricas_resultados_pc.xlsx
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>44.69</v>
+        <v>44.6</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>74.11</v>
+        <v>74.23</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
@@ -3033,16 +3033,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="C12" t="n">
-        <v>634</v>
+        <v>674</v>
       </c>
       <c r="D12" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="E12" t="n">
-        <v>3063</v>
+        <v>3260</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>13.26</v>
+        <v>13.42</v>
       </c>
     </row>
   </sheetData>
@@ -3415,16 +3415,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3063</v>
+        <v>3260</v>
       </c>
       <c r="C12" t="n">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="D12" t="n">
-        <v>21182</v>
+        <v>22509</v>
       </c>
       <c r="E12" t="n">
-        <v>44.69</v>
+        <v>44.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -4039,13 +4039,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="D12" t="n">
-        <v>74.11</v>
+        <v>74.23</v>
       </c>
       <c r="E12" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -4063,17 +4063,17 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="J12" t="n">
         <v>70</v>
       </c>
       <c r="K12" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
-          <t>missing-function-docstring: 39; trailing-whitespace: 21; no-member: 16; broad-exception-caught: 11; unused-import: 9; unexpected-keyword-arg: 9; 6/5: 8; 104/100: 7; undefined-variable: 6; protected-access: 5</t>
+          <t>missing-function-docstring: 39; trailing-whitespace: 26; no-member: 16; unexpected-keyword-arg: 16; broad-exception-caught: 11; 6/5: 10; 104/100: 7; unused-import: 6; undefined-variable: 6; protected-access: 5</t>
         </is>
       </c>
     </row>

--- a/medidor de metricas/automatizacion_completa/metricas_resultados_pc.xlsx
+++ b/medidor de metricas/automatizacion_completa/metricas_resultados_pc.xlsx
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>44.6</v>
+        <v>44.55</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>74.23</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
@@ -3033,16 +3033,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C12" t="n">
-        <v>674</v>
+        <v>686</v>
       </c>
       <c r="D12" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="E12" t="n">
-        <v>3260</v>
+        <v>3365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>13.42</v>
+        <v>13.79</v>
       </c>
     </row>
   </sheetData>
@@ -3415,16 +3415,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3260</v>
+        <v>3365</v>
       </c>
       <c r="C12" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D12" t="n">
-        <v>22509</v>
+        <v>22877</v>
       </c>
       <c r="E12" t="n">
-        <v>44.6</v>
+        <v>44.55</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -4039,13 +4039,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D12" t="n">
-        <v>74.23</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -4063,17 +4063,17 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J12" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K12" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
-          <t>missing-function-docstring: 39; trailing-whitespace: 26; no-member: 16; unexpected-keyword-arg: 16; broad-exception-caught: 11; 6/5: 10; 104/100: 7; unused-import: 6; undefined-variable: 6; protected-access: 5</t>
+          <t>missing-function-docstring: 39; trailing-whitespace: 26; no-member: 16; unexpected-keyword-arg: 16; broad-exception-caught: 11; 6/5: 10; 104/100: 7; undefined-variable: 6; protected-access: 5; 106/100: 4</t>
         </is>
       </c>
     </row>

--- a/medidor de metricas/automatizacion_completa/metricas_resultados_pc.xlsx
+++ b/medidor de metricas/automatizacion_completa/metricas_resultados_pc.xlsx
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>44.55</v>
+        <v>43.94</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>71.31999999999999</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
@@ -3033,16 +3033,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C12" t="n">
-        <v>686</v>
+        <v>701</v>
       </c>
       <c r="D12" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="E12" t="n">
-        <v>3365</v>
+        <v>3432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>13.79</v>
+        <v>13.89</v>
       </c>
     </row>
   </sheetData>
@@ -3415,16 +3415,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3365</v>
+        <v>3432</v>
       </c>
       <c r="C12" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D12" t="n">
-        <v>22877</v>
+        <v>23766</v>
       </c>
       <c r="E12" t="n">
-        <v>44.55</v>
+        <v>43.94</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -4039,13 +4039,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="D12" t="n">
-        <v>71.31999999999999</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -4063,17 +4063,17 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K12" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
-          <t>missing-function-docstring: 39; trailing-whitespace: 26; no-member: 16; unexpected-keyword-arg: 16; broad-exception-caught: 11; 6/5: 10; 104/100: 7; undefined-variable: 6; protected-access: 5; 106/100: 4</t>
+          <t>missing-function-docstring: 39; trailing-whitespace: 32; no-member: 16; unexpected-keyword-arg: 16; broad-exception-caught: 11; 6/5: 10; 104/100: 7; undefined-variable: 6; 106/100: 5; protected-access: 5</t>
         </is>
       </c>
     </row>
